--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484783_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484783_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6037</v>
+        <v>3.6444</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1735</v>
+        <v>4.1348</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5698</v>
+        <v>-0.4904</v>
       </c>
       <c r="G2" t="n">
         <v>0.595</v>
@@ -610,13 +610,13 @@
         <v>1.3209</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4426</v>
+        <v>0.4834</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4267</v>
+        <v>0.3881</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0159</v>
+        <v>0.0953</v>
       </c>
       <c r="V2" t="n">
         <v>1.2452</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5834</v>
+        <v>3.1756</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8629</v>
+        <v>4.3757</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2795</v>
+        <v>-1.2001</v>
       </c>
       <c r="G3" t="n">
         <v>1.7952</v>
@@ -688,13 +688,13 @@
         <v>1.5096</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2786</v>
+        <v>-0.1292</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4173</v>
+        <v>-0.0699</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1387</v>
+        <v>-0.0593</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4426</v>
+        <v>1.1613</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1132</v>
+        <v>1.3081</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3293</v>
+        <v>-0.1468</v>
       </c>
       <c r="G4" t="n">
         <v>2.9075</v>
@@ -766,13 +766,13 @@
         <v>1.1322</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2334</v>
+        <v>-0.0479</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5291</v>
+        <v>-0.3342</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7625</v>
+        <v>0.2863</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4285</v>
+        <v>0.5524</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.1897</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3362</v>
+        <v>0.3627</v>
       </c>
       <c r="G5" t="n">
         <v>0.4109</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0176</v>
+        <v>0.1415</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0711</v>
+        <v>0.1686</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0535</v>
+        <v>-0.027</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.0592</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3103</v>
+        <v>-0.2129</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2331</v>
+        <v>0.1537</v>
       </c>
       <c r="G7" t="n">
         <v>0.5541</v>
@@ -1000,13 +1000,13 @@
         <v>0.3774</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0472</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1052</v>
+        <v>-0.0078</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04</v>
+        <v>-0.0394</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4649</v>
+        <v>-2.2352</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1653</v>
+        <v>-1.0678</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2997</v>
+        <v>-1.1674</v>
       </c>
       <c r="G8" t="n">
         <v>-1.945</v>
@@ -1078,13 +1078,13 @@
         <v>0.5661</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7842</v>
+        <v>-0.5545</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2816</v>
+        <v>-0.1842</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5026</v>
+        <v>-0.3703</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3018</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. SARRIAS SANCHEZ</t>
+          <t>T. GOODMAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7228</v>
+        <v>-2.4439</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6281</v>
+        <v>0.2357</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0947</v>
+        <v>-2.6795</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.9051</v>
+        <v>0.8097</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.7496</v>
+        <v>-1.44</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1555</v>
+        <v>2.2496</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4624</v>
+        <v>3.9258</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7177</v>
+        <v>1.8281</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2553</v>
+        <v>2.0976</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.4427</v>
+        <v>-3.1161</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.0319</v>
+        <v>-3.2681</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4108</v>
+        <v>0.152</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3209</v>
+        <v>-4.1514</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9435</v>
+        <v>-6.6045</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2644</v>
+        <v>2.4531</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3839</v>
+        <v>-0.0455</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4674</v>
+        <v>-0.1796</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0835</v>
+        <v>0.1341</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2452</v>
+        <v>0.9434</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2452</v>
+        <v>3.094</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.1506</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. GOODMAN</t>
+          <t>D. SARRIAS SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0079</v>
+        <v>-2.646</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4077</v>
+        <v>-0.4718</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6002</v>
+        <v>-2.1741</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8097</v>
+        <v>-4.9051</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.44</v>
+        <v>-4.7496</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2496</v>
+        <v>-0.1555</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9258</v>
+        <v>-0.4624</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8281</v>
+        <v>-0.7177</v>
       </c>
       <c r="L10" t="n">
-        <v>2.0976</v>
+        <v>0.2553</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.1161</v>
+        <v>-4.4427</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.2681</v>
+        <v>-4.0319</v>
       </c>
       <c r="O10" t="n">
-        <v>0.152</v>
+        <v>-0.4108</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.1514</v>
+        <v>1.3209</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.6045</v>
+        <v>-0.9435</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4531</v>
+        <v>2.2644</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6096</v>
+        <v>-0.307</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.823</v>
+        <v>-0.3112</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2135</v>
+        <v>0.0042</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9434</v>
+        <v>1.2452</v>
       </c>
       <c r="W10" t="n">
-        <v>3.094</v>
+        <v>1.2452</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2534</v>
+        <v>-3.2836</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2277</v>
+        <v>-1.3638</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0256</v>
+        <v>-1.9198</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2461</v>
@@ -1312,13 +1312,13 @@
         <v>1.6983</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0118</v>
+        <v>-0.0185</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0029</v>
+        <v>-0.1332</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0089</v>
+        <v>0.1147</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8868</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. FERRAGUT SEBASTIA</t>
+          <t>L. CARRION GALINDO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1754</v>
+        <v>-3.7265</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2257</v>
+        <v>-1.645</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9497</v>
+        <v>-2.0815</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.3445</v>
+        <v>-2.5596</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.9035</v>
+        <v>-3.7353</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5589</v>
+        <v>1.1757</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0477</v>
+        <v>0.7123</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2207</v>
+        <v>-1.3938</v>
       </c>
       <c r="L12" t="n">
-        <v>0.173</v>
+        <v>2.1062</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2968</v>
+        <v>-3.2719</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.6827</v>
+        <v>-2.3415</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3859</v>
+        <v>-0.9304</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5096</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.8305</v>
+        <v>-3.774</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8483000000000001</v>
+        <v>-0.1477</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6525</v>
+        <v>0.1715</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1958</v>
+        <v>-0.3191</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1696</v>
+        <v>1.2452</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. CARRION GALINDO</t>
+          <t>A. FERRAGUT SEBASTIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2795</v>
+        <v>-4.7684</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8012</v>
+        <v>-2.7129</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4783</v>
+        <v>-2.0555</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.5596</v>
+        <v>-1.3445</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.7353</v>
+        <v>-2.9035</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1757</v>
+        <v>1.5589</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7123</v>
+        <v>-0.0477</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3938</v>
+        <v>-0.2207</v>
       </c>
       <c r="L13" t="n">
-        <v>2.1062</v>
+        <v>0.173</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.2719</v>
+        <v>-1.2968</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.3415</v>
+        <v>-2.6827</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9304</v>
+        <v>1.3859</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2644</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.774</v>
+        <v>-2.8305</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7007</v>
+        <v>0.2553</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0152</v>
+        <v>0.1653</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.716</v>
+        <v>0.09</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2452</v>
+        <v>-2.1696</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-2.1696</v>
       </c>
     </row>
     <row r="14">
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.606</v>
+        <v>-10.3121</v>
       </c>
       <c r="E14" t="n">
-        <v>2.792900000000001</v>
+        <v>3.086800000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.3989</v>
+        <v>-13.3987</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.6109</v>
+        <v>-3.610899999999999</v>
       </c>
       <c r="H14" t="n">
         <v>-17.4677</v>
@@ -1534,7 +1534,7 @@
         <v>-20.7308</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8626000000000004</v>
+        <v>-0.8626</v>
       </c>
       <c r="P14" t="n">
         <v>-6.6045</v>
@@ -1546,13 +1546,13 @@
         <v>14.1525</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7112999999999997</v>
+        <v>-0.4172999999999998</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6206</v>
+        <v>-0.3266</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.09070000000000011</v>
+        <v>-0.09050000000000005</v>
       </c>
       <c r="V14" t="n">
         <v>0.3208000000000002</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.603199999999999</v>
+        <v>9.2316</v>
       </c>
       <c r="E15" t="n">
-        <v>9.7996</v>
+        <v>9.507300000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1964</v>
+        <v>-0.2757</v>
       </c>
       <c r="G15" t="n">
         <v>5.8912</v>
@@ -1624,13 +1624,13 @@
         <v>2.6418</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4667</v>
+        <v>0.0951</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3585</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1082</v>
+        <v>0.0289</v>
       </c>
       <c r="V15" t="n">
         <v>1.547</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3968</v>
+        <v>5.5184</v>
       </c>
       <c r="E16" t="n">
-        <v>6.8932</v>
+        <v>6.9907</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4964</v>
+        <v>-1.4723</v>
       </c>
       <c r="G16" t="n">
         <v>1.6538</v>
@@ -1702,13 +1702,13 @@
         <v>2.6418</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1769</v>
+        <v>0.2985</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0436</v>
+        <v>0.0539</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2205</v>
+        <v>0.2446</v>
       </c>
       <c r="V16" t="n">
         <v>1.8678</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4081</v>
+        <v>2.2567</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4821</v>
+        <v>0.677</v>
       </c>
       <c r="F17" t="n">
-        <v>1.926</v>
+        <v>1.5798</v>
       </c>
       <c r="G17" t="n">
         <v>0.8662</v>
@@ -1780,13 +1780,13 @@
         <v>1.1322</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4098</v>
+        <v>0.2584</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2816</v>
+        <v>-0.0867</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6914</v>
+        <v>0.3451</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. MARTINEZ JURADO</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.88</v>
+        <v>1.0114</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6264999999999999</v>
+        <v>1.5798</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2535</v>
+        <v>-0.5683</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.294</v>
+        <v>-0.5484</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4431</v>
+        <v>0.3263</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8509</v>
+        <v>-0.8748</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4629</v>
+        <v>1.4655</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.019</v>
+        <v>0.1323</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4439</v>
+        <v>1.3332</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8311</v>
+        <v>-2.0139</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4241</v>
+        <v>0.1941</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4069</v>
+        <v>-2.208</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0757</v>
+        <v>1.1322</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0757</v>
+        <v>1.1322</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7964</v>
+        <v>0.4277</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7876</v>
+        <v>0.1143</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0089</v>
+        <v>0.3134</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>D. MARTÍNEZ JURADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4821</v>
+        <v>0.317</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9951</v>
+        <v>0.317</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5131</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5484</v>
+        <v>0.317</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3263</v>
+        <v>0.317</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8748</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4655</v>
+        <v>0.317</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1323</v>
+        <v>0.317</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3332</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0139</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1941</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.208</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1017</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4703</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3686</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. MARTÍNEZ JURADO</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.317</v>
+        <v>0.1949</v>
       </c>
       <c r="E20" t="n">
-        <v>0.317</v>
+        <v>-0.6242</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>0.317</v>
+        <v>-1.3521</v>
       </c>
       <c r="H20" t="n">
-        <v>0.317</v>
+        <v>1.9479</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-3.3</v>
       </c>
       <c r="J20" t="n">
-        <v>0.317</v>
+        <v>0.0192</v>
       </c>
       <c r="K20" t="n">
-        <v>0.317</v>
+        <v>2.5833</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-2.5642</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-1.3713</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.6354</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.7358</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.2644</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.3034</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.074</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>D. MARTINEZ JURADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4065</v>
+        <v>-0.1509</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0139</v>
+        <v>-0.6402</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6075</v>
+        <v>0.4892</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3521</v>
+        <v>-3.294</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9479</v>
+        <v>-1.4431</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.3</v>
+        <v>-1.8509</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0192</v>
+        <v>-1.4629</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5833</v>
+        <v>-1.019</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.5642</v>
+        <v>-0.4439</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3713</v>
+        <v>-1.8311</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6354</v>
+        <v>-0.4241</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7358</v>
+        <v>-1.4069</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3774</v>
+        <v>2.0757</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2644</v>
+        <v>2.0757</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9788</v>
+        <v>0.7655</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6931</v>
+        <v>0.5209</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2857</v>
+        <v>0.2446</v>
       </c>
       <c r="V21" t="n">
-        <v>1.547</v>
+        <v>0.3018</v>
       </c>
       <c r="W21" t="n">
-        <v>1.547</v>
+        <v>0.3018</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. CERVANTES GUERRA</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2786</v>
+        <v>-0.9596</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7447</v>
+        <v>1.3478</v>
       </c>
       <c r="F22" t="n">
-        <v>0.466</v>
+        <v>-2.3075</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2237</v>
+        <v>1.2665</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9626</v>
+        <v>5.6308</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1862</v>
+        <v>-4.3643</v>
       </c>
       <c r="J22" t="n">
-        <v>1.85</v>
+        <v>4.5158</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1097</v>
+        <v>6.2177</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7403</v>
+        <v>-1.7019</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0737</v>
+        <v>-3.2493</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1471</v>
+        <v>-0.5869</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9266</v>
+        <v>-2.6624</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.887</v>
+        <v>0.7548</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.774</v>
+        <v>-2.8305</v>
       </c>
       <c r="R22" t="n">
-        <v>1.887</v>
+        <v>3.5853</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1904</v>
+        <v>-0.1887</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1793</v>
+        <v>-0.3375</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0112</v>
+        <v>0.1488</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6415999999999999</v>
+        <v>-2.7922</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6415999999999999</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. MORATA</t>
+          <t>L. CERVANTES GUERRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5754</v>
+        <v>-1.2619</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1385</v>
+        <v>-1.9396</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5631</v>
+        <v>0.6777</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.246</v>
+        <v>-0.2237</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8695000000000001</v>
+        <v>0.9626</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6235000000000001</v>
+        <v>-1.1862</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3183</v>
+        <v>1.85</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3483</v>
+        <v>1.1097</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6666</v>
+        <v>0.7403</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5643</v>
+        <v>-2.0737</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5212</v>
+        <v>-0.1471</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0431</v>
+        <v>-1.9266</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3774</v>
+        <v>-1.887</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.8305</v>
+        <v>-3.774</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4531</v>
+        <v>1.887</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3104</v>
+        <v>0.2072</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0152</v>
+        <v>-0.0156</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3256</v>
+        <v>0.2228</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>E. MORATA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.6161</v>
+        <v>-1.3818</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0512</v>
+        <v>-3.2359</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6673</v>
+        <v>1.8541</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3342</v>
+        <v>-0.246</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2958</v>
+        <v>-0.8695000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.63</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.11</v>
+        <v>0.3183</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7184</v>
+        <v>-0.3483</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0.6666</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4442</v>
+        <v>-0.5643</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4226</v>
+        <v>-0.5212</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0216</v>
+        <v>-0.0431</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5661</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5661</v>
+        <v>2.4531</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.301</v>
+        <v>-0.1169</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0588</v>
+        <v>-0.0822</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2422</v>
+        <v>-0.0347</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.547</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.6333</v>
+        <v>-1.4922</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5683</v>
+        <v>0.1486</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2016</v>
+        <v>-1.6408</v>
       </c>
       <c r="G25" t="n">
-        <v>1.2665</v>
+        <v>-0.3342</v>
       </c>
       <c r="H25" t="n">
-        <v>5.6308</v>
+        <v>0.2958</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.3643</v>
+        <v>-0.63</v>
       </c>
       <c r="J25" t="n">
-        <v>4.5158</v>
+        <v>0.11</v>
       </c>
       <c r="K25" t="n">
-        <v>6.2177</v>
+        <v>0.7184</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.7019</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.2493</v>
+        <v>-0.4442</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.5869</v>
+        <v>-0.4226</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.6624</v>
+        <v>-0.0216</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7548</v>
+        <v>0.5661</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.5853</v>
+        <v>0.5661</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-0.1771</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.117</v>
+        <v>0.0386</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2546</v>
+        <v>-0.2157</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.7922</v>
+        <v>-1.547</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.7922</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.9713</v>
+        <v>-2.0279</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4372</v>
+        <v>-0.7295</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.5341</v>
+        <v>-1.2984</v>
       </c>
       <c r="G26" t="n">
         <v>-0.3851</v>
@@ -2482,13 +2482,13 @@
         <v>0.3774</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2251</v>
+        <v>0.1686</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4144</v>
+        <v>0.1221</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1893</v>
+        <v>0.0465</v>
       </c>
       <c r="V26" t="n">
         <v>-1.2452</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>10.606</v>
+        <v>11.2557</v>
       </c>
       <c r="E27" t="n">
-        <v>13.3987</v>
+        <v>13.3988</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.7928</v>
+        <v>-2.1431</v>
       </c>
       <c r="G27" t="n">
         <v>3.611200000000001</v>
@@ -2539,7 +2539,7 @@
         <v>20.7308</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8626</v>
+        <v>0.8625999999999995</v>
       </c>
       <c r="M27" t="n">
         <v>-17.9823</v>
@@ -2551,7 +2551,7 @@
         <v>-14.719</v>
       </c>
       <c r="P27" t="n">
-        <v>6.604500000000002</v>
+        <v>6.6045</v>
       </c>
       <c r="Q27" t="n">
         <v>-14.1525</v>
@@ -2560,16 +2560,16 @@
         <v>20.757</v>
       </c>
       <c r="S27" t="n">
-        <v>0.7110000000000002</v>
+        <v>1.3609</v>
       </c>
       <c r="T27" t="n">
         <v>0.09060000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>0.6206</v>
+        <v>1.2703</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.3207999999999993</v>
+        <v>-0.3208</v>
       </c>
       <c r="W27" t="n">
         <v>5.8672</v>
